--- a/server/data/openap/QBO-Openap.xlsx
+++ b/server/data/openap/QBO-Openap.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="570" windowWidth="19815" windowHeight="9150"/>
+    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="9405"/>
   </bookViews>
   <sheets>
     <sheet name="A P Aging Detail" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A P Aging Detail'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A P Aging Detail'!$A$1:$K$18</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -212,19 +212,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,426 +529,424 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" style="3" customWidth="1"/>
+    <col min="9" max="11" width="7.7109375" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>11986</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>518</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <v>3000</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="5">
         <v>3000</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="5">
         <v>3000</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>427</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <v>4074.84</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="5">
         <v>4074.84</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="5">
         <v>4074.84</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>427</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <v>-4124.84</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>-4124.84</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="5">
         <v>-4124.84</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>139</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <v>-2023.36</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>-0.25</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="5">
         <v>-0.25</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>106</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <v>5171.1400000000003</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>126.13</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="5">
         <v>120</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="5">
         <v>1.0510440000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>25</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <v>11940.98</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="5">
         <v>11940.98</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="5">
         <v>10500</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="5">
         <v>1.1372359999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>9</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <v>8430</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="5">
         <v>8430</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="5">
         <v>8430</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>9</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <v>12815.56</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="5">
         <v>12815.56</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="5">
         <v>12815.56</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>-6</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <v>13840</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="5">
         <v>13840</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="5">
         <v>13840</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>2099</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>-61</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <v>4700</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="5">
         <v>4700</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="5">
         <v>4700</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2">
+      <c r="E12" s="2"/>
+      <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <v>-1235.8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="5">
         <v>-1235.8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="5">
         <v>-1235.8</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="5">
         <v>1</v>
       </c>
     </row>
